--- a/CORTES DE CAJA/2026/6)JUNIO/LISTA DE LAS VENTAS SEMANA 24 DE JUNIO-26.xlsx
+++ b/CORTES DE CAJA/2026/6)JUNIO/LISTA DE LAS VENTAS SEMANA 24 DE JUNIO-26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B45AF7-FE55-4249-985A-5EE23577DE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A21D3CC-1B9D-407F-B00B-6F9374C1377E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1176,27 +1176,6 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1236,8 +1215,26 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1247,6 +1244,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1838,23 +1838,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -1867,14 +1867,14 @@
         <f>SUM(Tabla1[Importa])</f>
         <v>3310</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -1905,19 +1905,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>32</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -1936,21 +1936,21 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C36" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -1972,19 +1972,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>85.5</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -2006,19 +2006,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>67.5</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -2040,19 +2040,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -2074,19 +2074,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -2108,19 +2108,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>9</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -2142,19 +2142,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -2176,19 +2176,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>25.5</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -2207,19 +2207,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>75</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -2238,19 +2238,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>166</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -2272,17 +2272,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>148.5</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -2301,17 +2301,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>130</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -2330,17 +2330,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>115</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -2362,17 +2362,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>63</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -2394,17 +2394,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>351</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -2426,17 +2426,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>29</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -2458,17 +2458,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>9</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -2487,17 +2487,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>170</v>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -2520,7 +2520,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -2542,19 +2542,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>63</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -2573,17 +2573,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>40</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -2605,23 +2605,23 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G26))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>630</v>
       </c>
-      <c r="M26" s="38" t="s">
+      <c r="M26" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="38"/>
+      <c r="N26" s="31"/>
       <c r="O26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="P26" s="38" t="s">
+      <c r="P26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -2643,21 +2643,21 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G27))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>360</v>
       </c>
-      <c r="M27" s="26" t="s">
+      <c r="M27" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="N27" s="27"/>
-      <c r="O27" s="30">
+      <c r="N27" s="20"/>
+      <c r="O27" s="23">
         <v>1411</v>
       </c>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="34"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="27"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -2679,17 +2679,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G28))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M28" s="28"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="36"/>
-      <c r="R28" s="37"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="30"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -2711,17 +2711,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G29))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>72</v>
       </c>
-      <c r="M29" s="26"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="34"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="27"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -2743,17 +2743,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G30))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>18</v>
       </c>
-      <c r="M30" s="28"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="31"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="36"/>
-      <c r="R30" s="37"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="30"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
@@ -2775,17 +2775,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G31))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>76</v>
       </c>
-      <c r="M31" s="26"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="34"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="27"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
@@ -2807,17 +2807,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G32))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>85.5</v>
       </c>
-      <c r="M32" s="28"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="37"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="30"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
@@ -2839,17 +2839,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G33))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M33" s="26"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="32"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="34"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="23"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="27"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C34">
         <f t="shared" si="0"/>
@@ -2871,17 +2871,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G34))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M34" s="28"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="37"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="30"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
@@ -2903,17 +2903,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G35))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>87.5</v>
       </c>
-      <c r="M35" s="26"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="30"/>
-      <c r="P35" s="32"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="34"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="27"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
@@ -2932,12 +2932,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G36))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M36" s="28"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="36"/>
-      <c r="R36" s="37"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="30"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -2952,12 +2952,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G37))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M37" s="26"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="32"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="34"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="27"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -2972,12 +2972,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G38))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M38" s="28"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="36"/>
-      <c r="R38" s="37"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="30"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -2992,12 +2992,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G39))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M39" s="26"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="30"/>
-      <c r="P39" s="32"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="34"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="27"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -3012,12 +3012,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G40))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M40" s="28"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="36"/>
-      <c r="R40" s="37"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="30"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -3032,12 +3032,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G41))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M41" s="26"/>
-      <c r="N41" s="27"/>
-      <c r="O41" s="30"/>
-      <c r="P41" s="32"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="34"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="25"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="27"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -3052,12 +3052,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G42))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M42" s="28"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="35"/>
-      <c r="Q42" s="36"/>
-      <c r="R42" s="37"/>
+      <c r="M42" s="21"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="30"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -3072,12 +3072,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G43))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M43" s="26"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="34"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="23"/>
+      <c r="P43" s="25"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="27"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -3092,12 +3092,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G44))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M44" s="28"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="31"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="36"/>
-      <c r="R44" s="37"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="29"/>
+      <c r="R44" s="30"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -3112,12 +3112,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G45))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M45" s="26"/>
-      <c r="N45" s="27"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="32"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="34"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="23"/>
+      <c r="P45" s="25"/>
+      <c r="Q45" s="26"/>
+      <c r="R45" s="27"/>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="18" t="str">
@@ -3132,12 +3132,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G46))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M46" s="28"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="36"/>
-      <c r="R46" s="37"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="30"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="18" t="str">
@@ -3152,12 +3152,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G47))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M47" s="26"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="32"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="34"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="23"/>
+      <c r="P47" s="25"/>
+      <c r="Q47" s="26"/>
+      <c r="R47" s="27"/>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="str">
@@ -3172,12 +3172,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G48))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M48" s="28"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="35"/>
-      <c r="Q48" s="36"/>
-      <c r="R48" s="37"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="30"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" s="18" t="str">
@@ -3192,12 +3192,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G49))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M49" s="26"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="32"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="34"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="23"/>
+      <c r="P49" s="25"/>
+      <c r="Q49" s="26"/>
+      <c r="R49" s="27"/>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="18" t="str">
@@ -3212,12 +3212,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G50))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M50" s="28"/>
-      <c r="N50" s="29"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="35"/>
-      <c r="Q50" s="36"/>
-      <c r="R50" s="37"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="24"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="29"/>
+      <c r="R50" s="30"/>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="18" t="str">
@@ -3232,12 +3232,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G51))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M51" s="26"/>
-      <c r="N51" s="27"/>
-      <c r="O51" s="30"/>
-      <c r="P51" s="32"/>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="34"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="20"/>
+      <c r="O51" s="23"/>
+      <c r="P51" s="25"/>
+      <c r="Q51" s="26"/>
+      <c r="R51" s="27"/>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B52" s="18" t="str">
@@ -3252,12 +3252,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G52))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M52" s="28"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="31"/>
-      <c r="P52" s="35"/>
-      <c r="Q52" s="36"/>
-      <c r="R52" s="37"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="22"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="30"/>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="18" t="str">
@@ -3976,33 +3976,19 @@
   </sheetData>
   <autoFilter ref="B4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="48">
-    <mergeCell ref="M49:N50"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P49:R50"/>
-    <mergeCell ref="M51:N52"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="P51:R52"/>
-    <mergeCell ref="M45:N46"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="P45:R46"/>
-    <mergeCell ref="M47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:R48"/>
-    <mergeCell ref="P31:R32"/>
-    <mergeCell ref="P33:R34"/>
-    <mergeCell ref="P35:R36"/>
-    <mergeCell ref="P37:R38"/>
-    <mergeCell ref="P39:R40"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="O33:O34"/>
-    <mergeCell ref="O35:O36"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="M31:N32"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="M35:N36"/>
-    <mergeCell ref="M37:N38"/>
-    <mergeCell ref="M39:N40"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M41:N42"/>
+    <mergeCell ref="M43:N44"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="P41:R42"/>
+    <mergeCell ref="P43:R44"/>
     <mergeCell ref="P26:R26"/>
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="M27:N28"/>
@@ -4011,19 +3997,33 @@
     <mergeCell ref="O29:O30"/>
     <mergeCell ref="P27:R28"/>
     <mergeCell ref="P29:R30"/>
-    <mergeCell ref="M41:N42"/>
-    <mergeCell ref="M43:N44"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="P41:R42"/>
-    <mergeCell ref="P43:R44"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M31:N32"/>
+    <mergeCell ref="M33:N34"/>
+    <mergeCell ref="M35:N36"/>
+    <mergeCell ref="M37:N38"/>
+    <mergeCell ref="M39:N40"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="P31:R32"/>
+    <mergeCell ref="P33:R34"/>
+    <mergeCell ref="P35:R36"/>
+    <mergeCell ref="P37:R38"/>
+    <mergeCell ref="P39:R40"/>
+    <mergeCell ref="M45:N46"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="P45:R46"/>
+    <mergeCell ref="M47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:R48"/>
+    <mergeCell ref="M49:N50"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P49:R50"/>
+    <mergeCell ref="M51:N52"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="P51:R52"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="13" priority="1">
@@ -4063,23 +4063,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -4092,14 +4092,14 @@
         <f>SUM(Tabla110[Importa])</f>
         <v>1729.5</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -4130,19 +4130,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>17</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla110[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -4164,21 +4164,21 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>123.5</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -4200,19 +4200,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>140</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -4234,19 +4234,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -4268,19 +4268,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -4302,19 +4302,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>32.5</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -4336,19 +4336,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>32.5</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -4367,19 +4367,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>150</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -4398,19 +4398,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>32</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -4429,19 +4429,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>68</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -4463,19 +4463,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -4497,17 +4497,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>719.5</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -4529,17 +4529,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -4561,17 +4561,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>123.5</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -4593,17 +4593,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>32.5</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -4622,17 +4622,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>75</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -4654,17 +4654,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -4683,17 +4683,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>25</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -4703,17 +4703,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -4727,7 +4727,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -4737,19 +4737,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -4759,17 +4759,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -4785,17 +4785,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -4811,15 +4811,15 @@
       <c r="N27" s="15">
         <v>4259</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -4831,15 +4831,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -4851,15 +4851,15 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -4871,15 +4871,15 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -4891,15 +4891,15 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -4911,15 +4911,15 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -4931,15 +4931,15 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -4951,15 +4951,15 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -4971,15 +4971,15 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -4991,10 +4991,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -5011,10 +5011,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -5031,10 +5031,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -5051,10 +5051,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -5071,10 +5071,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -5091,10 +5091,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -5111,10 +5111,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -5131,10 +5131,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -5151,10 +5151,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -5984,32 +5984,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -6047,23 +6047,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -6076,14 +6076,14 @@
         <f>SUM(Tabla111[Importa])</f>
         <v>1550</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -6114,17 +6114,17 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>15</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla111[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -6143,21 +6143,21 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -6176,19 +6176,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>200</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C7">
         <f>IF(ISNUMBER(E7), IF(ISNUMBER(C6), C6+1, 1), "")</f>
@@ -6207,19 +6207,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>70</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C68" si="1">IF(ISNUMBER(E8), IF(ISNUMBER(C7), C7+1, 1), "")</f>
@@ -6238,19 +6238,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>105</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
@@ -6272,19 +6272,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -6306,19 +6306,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>4.5</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -6337,19 +6337,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>147</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -6368,19 +6368,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>147</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -6402,19 +6402,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -6436,19 +6436,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>25.5</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C15">
         <f t="shared" si="1"/>
@@ -6467,17 +6467,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>200</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C16">
         <f t="shared" si="1"/>
@@ -6496,17 +6496,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>200</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C17">
         <f t="shared" si="1"/>
@@ -6528,17 +6528,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>248.5</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C18">
         <f t="shared" si="1"/>
@@ -6560,17 +6560,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>58.5</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C19">
         <f t="shared" si="1"/>
@@ -6592,17 +6592,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="1"/>
@@ -6612,17 +6612,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="1"/>
@@ -6632,17 +6632,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="1"/>
@@ -6652,17 +6652,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="1"/>
@@ -6676,7 +6676,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="1"/>
@@ -6686,19 +6686,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="1"/>
@@ -6708,17 +6708,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="1"/>
@@ -6734,17 +6734,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="1"/>
@@ -6756,15 +6756,15 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="1"/>
@@ -6776,15 +6776,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="1"/>
@@ -6796,15 +6796,15 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="1"/>
@@ -6816,15 +6816,15 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="1"/>
@@ -6836,15 +6836,15 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="1"/>
@@ -6856,15 +6856,15 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="1"/>
@@ -6876,15 +6876,15 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="1"/>
@@ -6896,15 +6896,15 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="1"/>
@@ -6916,15 +6916,15 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="1"/>
@@ -6936,10 +6936,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -6956,10 +6956,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -6976,10 +6976,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -6996,10 +6996,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -7016,10 +7016,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -7036,10 +7036,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -7056,10 +7056,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -7076,10 +7076,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -7096,10 +7096,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -7929,32 +7929,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="9" priority="1">
@@ -7992,23 +7992,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -8021,14 +8021,14 @@
         <f>SUM(Tabla112[Importa])</f>
         <v>1836</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -8059,17 +8059,17 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>12</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla112[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -8091,21 +8091,21 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>160.5</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -8127,19 +8127,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>85.5</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -8161,19 +8161,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>53.5</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -8195,19 +8195,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>171</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -8226,19 +8226,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>25</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -8257,19 +8257,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -8291,19 +8291,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>237</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -8325,19 +8325,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>237</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -8359,19 +8359,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>34.5</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -8390,19 +8390,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>372</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -8421,17 +8421,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>320</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -8453,17 +8453,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>130</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -8473,17 +8473,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -8493,17 +8493,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -8513,17 +8513,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -8533,17 +8533,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -8553,17 +8553,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -8573,17 +8573,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -8597,7 +8597,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -8607,19 +8607,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -8629,17 +8629,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -8655,17 +8655,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -8677,15 +8677,15 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -8697,15 +8697,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -8717,15 +8717,15 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -8737,15 +8737,15 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -8757,15 +8757,15 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -8777,15 +8777,15 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -8797,15 +8797,15 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -8817,15 +8817,15 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -8837,15 +8837,15 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -8857,10 +8857,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -8877,10 +8877,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -8897,10 +8897,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -8917,10 +8917,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -8937,10 +8937,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -8957,10 +8957,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -8977,10 +8977,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -8997,10 +8997,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -9017,10 +9017,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -9850,32 +9850,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="7" priority="1">
@@ -9914,23 +9914,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -9943,14 +9943,14 @@
         <f>SUM(Tabla113[Importa])</f>
         <v>1932</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -9981,19 +9981,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>13</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla113[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -10012,21 +10012,21 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>130</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -10045,19 +10045,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>250</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -10076,19 +10076,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>16</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -10107,19 +10107,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>40</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -10138,19 +10138,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>280</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -10169,19 +10169,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>100</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -10200,19 +10200,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>60</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -10234,19 +10234,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>315</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -10268,19 +10268,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>81</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -10302,19 +10302,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -10336,17 +10336,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -10368,17 +10368,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>225</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -10397,17 +10397,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>345</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -10417,17 +10417,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -10437,17 +10437,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -10457,17 +10457,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -10477,17 +10477,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -10497,17 +10497,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -10521,7 +10521,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -10531,19 +10531,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -10553,17 +10553,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -10579,17 +10579,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -10605,17 +10605,17 @@
       <c r="N27" s="15">
         <v>1411</v>
       </c>
-      <c r="O27" s="40" t="s">
+      <c r="O27" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -10631,17 +10631,17 @@
       <c r="N28" s="15">
         <v>4259</v>
       </c>
-      <c r="O28" s="40" t="s">
+      <c r="O28" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -10657,17 +10657,17 @@
       <c r="N29" s="15">
         <v>1500</v>
       </c>
-      <c r="O29" s="40" t="s">
+      <c r="O29" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -10683,17 +10683,17 @@
       <c r="N30" s="15">
         <v>7170</v>
       </c>
-      <c r="O30" s="40" t="s">
+      <c r="O30" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -10705,15 +10705,15 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -10725,15 +10725,15 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -10745,15 +10745,15 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -10765,15 +10765,15 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -10785,15 +10785,15 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -10805,10 +10805,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -10825,10 +10825,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -10845,10 +10845,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -10865,10 +10865,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -10885,10 +10885,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -10905,10 +10905,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -10925,10 +10925,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -10945,10 +10945,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -10965,10 +10965,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -11798,32 +11798,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11862,23 +11862,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -11891,14 +11891,14 @@
         <f>SUM(Tabla114[Importa])</f>
         <v>3002</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -11932,16 +11932,16 @@
       <c r="M4" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla114[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -11960,21 +11960,21 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -11993,19 +11993,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -12024,19 +12024,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>147</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -12055,19 +12055,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>8</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -12086,19 +12086,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>225</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -12117,19 +12117,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>60</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -12151,19 +12151,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>342</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -12182,19 +12182,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>147</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -12213,19 +12213,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>190</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -12247,19 +12247,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>191</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -12281,17 +12281,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>121.5</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -12313,17 +12313,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -12342,17 +12342,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>150</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -12371,17 +12371,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -12400,17 +12400,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -12429,17 +12429,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>36</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -12461,17 +12461,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>630</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -12493,17 +12493,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>77.5</v>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -12526,7 +12526,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -12545,19 +12545,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>70</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -12576,17 +12576,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -12611,17 +12611,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -12646,15 +12646,15 @@
       <c r="N27" s="15">
         <v>5160</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -12675,15 +12675,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -12704,15 +12704,15 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
@@ -12733,15 +12733,15 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
@@ -12762,15 +12762,15 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -12782,15 +12782,15 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -12802,15 +12802,15 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -12822,15 +12822,15 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -12842,15 +12842,15 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -12862,10 +12862,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -12882,10 +12882,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -12902,10 +12902,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -12922,10 +12922,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -12942,10 +12942,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -12962,10 +12962,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -12982,10 +12982,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -13002,10 +13002,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -13022,10 +13022,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -13855,32 +13855,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -13918,23 +13918,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -13947,14 +13947,14 @@
         <f>SUM(Tabla115[Importa])</f>
         <v>0</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -13985,12 +13985,12 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="str">
@@ -14005,21 +14005,21 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -14029,19 +14029,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -14051,19 +14051,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -14073,19 +14073,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -14095,19 +14095,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -14117,19 +14117,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -14139,19 +14139,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -14161,19 +14161,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -14183,19 +14183,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -14205,19 +14205,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -14227,17 +14227,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -14247,17 +14247,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -14267,17 +14267,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -14287,17 +14287,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -14307,17 +14307,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -14327,17 +14327,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -14347,17 +14347,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -14367,17 +14367,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -14391,7 +14391,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -14401,19 +14401,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -14423,17 +14423,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -14449,17 +14449,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -14471,15 +14471,15 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -14491,15 +14491,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -14511,15 +14511,15 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -14531,15 +14531,15 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -14551,15 +14551,15 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -14571,15 +14571,15 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -14591,15 +14591,15 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -14611,15 +14611,15 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -14631,15 +14631,15 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46200.797616666663</v>
+        <v>46202.761779398148</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -14651,10 +14651,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -14671,10 +14671,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -14691,10 +14691,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -14711,10 +14711,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -14731,10 +14731,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -14751,10 +14751,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -14771,10 +14771,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -14791,10 +14791,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -14811,10 +14811,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -15644,32 +15644,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="1" priority="1">
